--- a/data/trans_orig/IP2002-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2002-Edad-trans_orig.xlsx
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>244580</t>
+          <t>244803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>251286</t>
+          <t>251300</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>244797</t>
+          <t>244757</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>251024</t>
+          <t>251634</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>492457</t>
+          <t>492184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>501557</t>
+          <t>501471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21624</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>14460</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28914</t>
+          <t>28470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27771</t>
+          <t>26737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45730</t>
+          <t>44705</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105924</t>
+          <t>105894</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117990</t>
+          <t>117626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112601</t>
+          <t>113045</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>126449</t>
+          <t>127055</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>223333</t>
+          <t>224358</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>241292</t>
+          <t>242326</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>90,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20376</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35822</t>
+          <t>35987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>33466</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>41463</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62632</t>
+          <t>63740</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158275</t>
+          <t>158110</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173721</t>
+          <t>173892</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172319</t>
+          <t>171903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>186950</t>
+          <t>186858</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>336834</t>
+          <t>335726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>358603</t>
+          <t>358003</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36410</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57038</t>
+          <t>58466</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40380</t>
+          <t>40242</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61774</t>
+          <t>62884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80403</t>
+          <t>81343</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111998</t>
+          <t>110831</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>588002</t>
+          <t>586574</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>609418</t>
+          <t>608630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>623249</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>644643</t>
+          <t>644781</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1218065</t>
+          <t>1219232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1249660</t>
+          <t>1248720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18091</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25516</t>
+          <t>25455</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>225281</t>
+          <t>225139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>233615</t>
+          <t>233331</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>250900</t>
+          <t>250789</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>262519</t>
+          <t>262713</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>479725</t>
+          <t>479786</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>494065</t>
+          <t>494527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>12098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25169</t>
+          <t>25925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22905</t>
+          <t>23241</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39919</t>
+          <t>39465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136720</t>
+          <t>136091</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148485</t>
+          <t>148610</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132662</t>
+          <t>131906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146447</t>
+          <t>145733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>274955</t>
+          <t>275409</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>291969</t>
+          <t>291633</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>23502</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14173</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28443</t>
+          <t>28158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28814</t>
+          <t>28246</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47963</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145485</t>
+          <t>147226</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159359</t>
+          <t>159673</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151512</t>
+          <t>151797</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165782</t>
+          <t>165923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302720</t>
+          <t>303676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>321869</t>
+          <t>322437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,95%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27367</t>
+          <t>28359</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47763</t>
+          <t>47592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38044</t>
+          <t>38542</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60920</t>
+          <t>60200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71459</t>
+          <t>71872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101364</t>
+          <t>103048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>615128</t>
+          <t>615299</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>635524</t>
+          <t>634532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>641779</t>
+          <t>642499</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>664655</t>
+          <t>664157</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1264227</t>
+          <t>1262543</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1294132</t>
+          <t>1293719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>550</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200130</t>
+          <t>199157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>207311</t>
+          <t>207273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>252413</t>
+          <t>252568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>257509</t>
+          <t>257511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>455195</t>
+          <t>454830</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>464038</t>
+          <t>464019</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13984</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27574</t>
+          <t>27923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20738</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42586</t>
+          <t>42765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>161325</t>
+          <t>160976</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>174915</t>
+          <t>174931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>168449</t>
+          <t>167834</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180192</t>
+          <t>179864</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334885</t>
+          <t>334706</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>352548</t>
+          <t>352724</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24438</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26454</t>
+          <t>26268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25658</t>
+          <t>25924</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45383</t>
+          <t>44555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148313</t>
+          <t>149992</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162224</t>
+          <t>161986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147594</t>
+          <t>147780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161953</t>
+          <t>161829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301416</t>
+          <t>302244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>321141</t>
+          <t>320875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>31165</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52486</t>
+          <t>52117</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45040</t>
+          <t>44593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61774</t>
+          <t>61321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90001</t>
+          <t>89220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>606345</t>
+          <t>606714</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>627430</t>
+          <t>627666</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>655855</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>674742</t>
+          <t>675609</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1269725</t>
+          <t>1270506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1297952</t>
+          <t>1298405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44413</t>
+          <t>44391</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92814</t>
+          <t>92777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12730</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>19134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>149343</t>
+          <t>149160</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156619</t>
+          <t>156531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>168833</t>
+          <t>167861</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>178290</t>
+          <t>178452</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>320220</t>
+          <t>321565</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>333309</t>
+          <t>333469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24727</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17377</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36161</t>
+          <t>36530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148345</t>
+          <t>149984</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>162517</t>
+          <t>163082</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>195113</t>
+          <t>195476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>206538</t>
+          <t>206681</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>349402</t>
+          <t>349033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>366420</t>
+          <t>366347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>10269</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27093</t>
+          <t>26941</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>12072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29062</t>
+          <t>28716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26540</t>
+          <t>26778</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51551</t>
+          <t>51424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>248365</t>
+          <t>248517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>264750</t>
+          <t>265189</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>276421</t>
+          <t>276767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>292816</t>
+          <t>293411</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>529389</t>
+          <t>529516</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>554400</t>
+          <t>554162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>28474</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51005</t>
+          <t>50197</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27882</t>
+          <t>27386</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50173</t>
+          <t>49894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62221</t>
+          <t>61602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93246</t>
+          <t>92702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>605066</t>
+          <t>605874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>626842</t>
+          <t>627597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>697292</t>
+          <t>697571</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>719583</t>
+          <t>720079</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1310290</t>
+          <t>1310834</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1341315</t>
+          <t>1341934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2002-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2002-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>85108</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>70767</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>85108</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85108</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85108</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85108</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70767</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70767</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70767</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85108</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>85108</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>85108</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8388</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3593</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7826</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7809</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4102</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1397</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8274</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>248929</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>244643</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>251653</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>373</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>249036</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>244803</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>251300</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>244820</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>251302</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,58%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,91%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,47%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>248929</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>244757</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>251634</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>748</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>492184</t>
+          <t>492338</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>501471</t>
+          <t>501542</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253031</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253031</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253031</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>252629</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>252629</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>252629</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253031</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253031</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253031</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20494</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14148</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28120</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>15163</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9922</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21654</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9176</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20604</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,89%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20494</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14460</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>28470</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26737</t>
+          <t>27596</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44705</t>
+          <t>44657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>121021</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>113395</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>127367</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>85,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>112385</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>105894</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>117626</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>106944</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>118372</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,11%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,22%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>121021</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>113045</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>127055</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>85,52%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>224358</t>
+          <t>224406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>242326</t>
+          <t>241467</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25283</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19077</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34336</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>27065</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20205</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35987</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>20133</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35153</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,94%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>25283</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18511</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>33466</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41463</t>
+          <t>41888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63740</t>
+          <t>64208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>180086</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>171033</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>186292</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,28%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>167032</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>158110</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>173892</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>158944</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>173964</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,06%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>180086</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>171903</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>186858</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>335726</t>
+          <t>335258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>358003</t>
+          <t>357578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205369</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205369</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205369</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205369</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205369</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205369</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>49879</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40464</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63034</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>45821</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>36410</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>58466</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35874</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>57442</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,1%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>49879</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>40242</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>62884</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81343</t>
+          <t>81953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110831</t>
+          <t>111232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>635144</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>621989</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>644559</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,8%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>895</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>599219</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>586574</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>608630</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>587598</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>609166</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>92,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>635144</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>622139</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>644781</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1219232</t>
+          <t>1218831</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1248720</t>
+          <t>1248110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>685023</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>685023</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>685023</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>963</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>645040</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>645040</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>645040</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>685023</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>685023</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>685023</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>98870</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11318</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6211</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18378</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5896</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2919</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11111</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2867</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11639</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11318</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18202</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>10851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25455</t>
+          <t>25747</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>257673</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>250613</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>262780</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,79%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>230354</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>225139</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>233331</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>224611</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>233383</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,5%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>257673</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>250789</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>262713</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>479786</t>
+          <t>479494</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>494527</t>
+          <t>494390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17326</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11573</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24921</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>13700</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8433</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20952</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8708</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20744</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>8,72%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17326</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12098</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>25925</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23241</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39465</t>
+          <t>40678</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -3474,67 +3474,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>140505</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>132910</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>146258</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>143343</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>136091</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148610</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>136299</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>148335</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>91,28%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,66%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140505</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>131906</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>145733</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,02%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>275409</t>
+          <t>274196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>291633</t>
+          <t>291888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>157831</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>157831</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157831</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>157831</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>157831</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>157831</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20039</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14011</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27642</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,14%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>17076</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11055</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23502</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>11416</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24350</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20039</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14032</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>28158</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28246</t>
+          <t>28119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47007</t>
+          <t>47460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>159916</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>152313</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>165944</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>153652</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>147226</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>159673</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>146378</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>159312</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>159916</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>151797</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>165923</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>88,86%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>303676</t>
+          <t>303223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322437</t>
+          <t>322564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170728</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170728</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170728</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>48684</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37611</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>60864</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>36672</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28359</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47592</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>27318</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>46356</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,53%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>48684</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>38542</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>60200</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71872</t>
+          <t>71434</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103048</t>
+          <t>100916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>654015</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>641835</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>665088</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,07%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,34%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>901</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>626219</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>615299</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>634532</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>616535</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>635573</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,47%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,82%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>654015</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>642499</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>664157</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,07%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1262543</t>
+          <t>1264675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1293719</t>
+          <t>1294157</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>702699</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>702699</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>702699</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>662891</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>662891</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>662891</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>702699</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>702699</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>702699</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>87859</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5982</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4740</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10164</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,26%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2090</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5493</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>255971</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>252079</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>257516</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>323</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>204581</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>199157</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>207273</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>199216</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>207261</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,74%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,02%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>255971</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>252568</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>257511</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,79%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>700</t>
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>454830</t>
+          <t>454942</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>464019</t>
+          <t>463831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>209321</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>209321</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>209321</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13484</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8454</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20956</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>19757</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13968</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27923</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13396</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26732</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,46%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13484</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8708</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>20738</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>24494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42765</t>
+          <t>42910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -5421,67 +5421,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>175088</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>167616</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>180118</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,85%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>169142</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>160976</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>174931</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>162167</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>175503</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,54%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>175088</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>167834</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>179864</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,85%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334706</t>
+          <t>334561</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>352724</t>
+          <t>352977</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,67 +5651,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>18142</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12049</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25776</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>16436</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10765</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22759</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10791</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23462</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,51%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>18142</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12219</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>26268</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25924</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44555</t>
+          <t>45212</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>155906</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>148272</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>161999</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>156315</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>149992</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>161986</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>149289</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>161960</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>155906</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>147780</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>161829</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,58%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302244</t>
+          <t>301587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>320875</t>
+          <t>321089</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172751</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172751</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172751</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33716</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25408</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>43923</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>40933</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>31165</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>52117</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>31333</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>51664</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33716</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>25286</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>44593</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61321</t>
+          <t>61818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89220</t>
+          <t>89187</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>667179</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>656972</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>675487</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,37%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>617898</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>606714</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>627666</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>607167</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>627498</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>93,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,09%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>954</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>667179</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>656302</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>675609</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1270506</t>
+          <t>1270539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1298405</t>
+          <t>1297908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>988</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>658831</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>658831</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>658831</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3070</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3538</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3557</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39111</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36606</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,26%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>44563</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>47222</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>44391</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>47929</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>92,62%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>175</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>95627</t>
+          <t>83674</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92777</t>
+          <t>81389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>11361</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>18662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>150688</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>145419</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>153858</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,16%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>153802</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>149160</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>156531</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>174674</t>
+          <t>139720</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>167861</t>
+          <t>134794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>178452</t>
+          <t>142676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>328476</t>
+          <t>290408</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>321565</t>
+          <t>283107</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>333469</t>
+          <t>295030</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156744</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156744</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156744</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159136</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159136</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159136</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181563</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181563</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181563</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>340699</t>
+          <t>301769</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>340699</t>
+          <t>301769</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>340699</t>
+          <t>301769</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9575</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5208</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16873</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>15979</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9990</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23088</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>16242</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>23290</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26525</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19216</t>
+          <t>18123</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36530</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>190551</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>183253</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>194918</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>157093</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>149984</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>163082</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>90,77%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,66%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>201944</t>
+          <t>158430</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>195476</t>
+          <t>151382</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>206681</t>
+          <t>164441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>359038</t>
+          <t>348981</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>349033</t>
+          <t>339907</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>366347</t>
+          <t>356675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26941</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,67 +7633,67 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19375</t>
+          <t>16733</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12072</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28716</t>
+          <t>24306</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>9,47%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>34832</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>25392</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>46583</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>6,34%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>36911</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>26778</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>51424</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>257922</t>
+          <t>274547</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>248517</t>
+          <t>266192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265189</t>
+          <t>281343</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,67 +7746,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>286108</t>
+          <t>239820</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>276767</t>
+          <t>232247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>293411</t>
+          <t>245969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>90,53%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>514366</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>502615</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>523806</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>93,66%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>90,6%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>96,05%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>544029</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>529516</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>554162</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34294</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24835</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46040</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>38849</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28474</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>50197</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>38281</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>28520</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49894</t>
+          <t>49187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>76367</t>
+          <t>72575</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61602</t>
+          <t>59739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92702</t>
+          <t>89200</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>654896</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>643150</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>664355</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>867</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>617222</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>605874</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>627597</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,66%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>899</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>709947</t>
+          <t>582533</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>697571</t>
+          <t>571627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720079</t>
+          <t>592294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1327169</t>
+          <t>1237429</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1310834</t>
+          <t>1220804</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1341934</t>
+          <t>1250265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>921</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
